--- a/public/magnolia/special.xlsx
+++ b/public/magnolia/special.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF075C25-3A89-1649-8C0F-535F65B4AEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9496A515-7C11-744E-A0C2-4E8E32FD5933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="620" windowWidth="13560" windowHeight="16260" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="600" windowWidth="13560" windowHeight="16260" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
   <si>
     <t>name_ru</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Бриошь с бананом и карамелью</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Brioche with Banana &amp; Caramel</t>
@@ -1060,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65221F5B-7B4E-674E-92C0-A7DEAD7F14CD}">
-  <dimension ref="A1:AD998"/>
+  <dimension ref="A1:AD997"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:30" ht="19" x14ac:dyDescent="0.25">
@@ -1187,11 +1184,11 @@
         <v>30</v>
       </c>
       <c r="I3" s="29" t="str">
-        <f t="shared" ref="I3:I15" si="0">LOWER($B3)</f>
+        <f t="shared" ref="I3:I14" si="0">LOWER($B3)</f>
         <v>gnocchi with pesto cream &amp; sun-dried tomatoes</v>
       </c>
       <c r="J3" s="29" t="str">
-        <f t="shared" ref="J3:J16" si="1">LOWER($B3)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J3:J5" si="1">LOWER($B3)&amp;"_"&amp;2</f>
         <v>gnocchi with pesto cream &amp; sun-dried tomatoes_2</v>
       </c>
       <c r="K3" s="26"/>
@@ -1265,23 +1262,23 @@
         <v>37</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="27">
         <v>14</v>
       </c>
       <c r="F5" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="H5" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="I5" s="29" t="str">
         <f t="shared" si="0"/>
@@ -1314,9 +1311,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="27"/>
-      <c r="B6" s="27" t="s">
-        <v>38</v>
-      </c>
+      <c r="B6" s="27"/>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="28"/>
@@ -1325,7 +1320,7 @@
       <c r="H6" s="29"/>
       <c r="I6" s="29" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="J6" s="29"/>
       <c r="K6" s="26"/>
@@ -1345,7 +1340,6 @@
       <c r="Y6" s="26"/>
       <c r="Z6" s="26"/>
       <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
@@ -1384,7 +1378,7 @@
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="27"/>
       <c r="G8" s="27"/>
       <c r="H8" s="29"/>
@@ -1393,23 +1387,24 @@
         <v/>
       </c>
       <c r="J8" s="29"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="27"/>
@@ -1417,16 +1412,16 @@
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J9" s="29"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
       <c r="M9" s="29"/>
       <c r="N9" s="29"/>
       <c r="O9" s="29"/>
@@ -1442,7 +1437,6 @@
       <c r="Y9" s="29"/>
       <c r="Z9" s="29"/>
       <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="27"/>
@@ -1450,7 +1444,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="30"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="30"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29" t="str">
@@ -1475,15 +1469,16 @@
       <c r="Y10" s="29"/>
       <c r="Z10" s="29"/>
       <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="30"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="29" t="str">
         <f t="shared" si="0"/>
@@ -1507,7 +1502,6 @@
       <c r="Y11" s="29"/>
       <c r="Z11" s="29"/>
       <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="27"/>
@@ -1543,8 +1537,8 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="27"/>
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
@@ -1574,10 +1568,10 @@
       <c r="AA13" s="29"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="27"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="26"/>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
       <c r="G14" s="29"/>
@@ -1604,20 +1598,20 @@
       <c r="Y14" s="29"/>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="26"/>
       <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="26"/>
       <c r="E15" s="29"/>
       <c r="F15" s="29"/>
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
-      <c r="I15" s="29" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I15" s="29"/>
       <c r="J15" s="29"/>
       <c r="K15" s="29"/>
       <c r="L15" s="29"/>
@@ -1739,7 +1733,7 @@
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="26"/>
       <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="26"/>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
@@ -1771,7 +1765,7 @@
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
-      <c r="C20" s="27"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="26"/>
       <c r="E20" s="29"/>
       <c r="F20" s="29"/>
@@ -33063,38 +33057,6 @@
       <c r="AB997" s="29"/>
       <c r="AC997" s="29"/>
       <c r="AD997" s="29"/>
-    </row>
-    <row r="998" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A998" s="26"/>
-      <c r="B998" s="26"/>
-      <c r="C998" s="26"/>
-      <c r="D998" s="26"/>
-      <c r="E998" s="29"/>
-      <c r="F998" s="29"/>
-      <c r="G998" s="29"/>
-      <c r="H998" s="29"/>
-      <c r="I998" s="29"/>
-      <c r="J998" s="29"/>
-      <c r="K998" s="29"/>
-      <c r="L998" s="29"/>
-      <c r="M998" s="29"/>
-      <c r="N998" s="29"/>
-      <c r="O998" s="29"/>
-      <c r="P998" s="29"/>
-      <c r="Q998" s="29"/>
-      <c r="R998" s="29"/>
-      <c r="S998" s="29"/>
-      <c r="T998" s="29"/>
-      <c r="U998" s="29"/>
-      <c r="V998" s="29"/>
-      <c r="W998" s="29"/>
-      <c r="X998" s="29"/>
-      <c r="Y998" s="29"/>
-      <c r="Z998" s="29"/>
-      <c r="AA998" s="29"/>
-      <c r="AB998" s="29"/>
-      <c r="AC998" s="29"/>
-      <c r="AD998" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33147,26 +33109,26 @@
     </row>
     <row r="2" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="12">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I2" s="14" t="str">
         <f t="shared" ref="I2:I13" si="0">LOWER($B2)</f>
@@ -33179,26 +33141,26 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="12">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33211,26 +33173,26 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="12">
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I4" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33243,26 +33205,26 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="12">
         <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="13" t="s">
         <v>78</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>79</v>
       </c>
       <c r="I5" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33275,26 +33237,26 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="H6" s="13" t="s">
         <v>81</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>82</v>
       </c>
       <c r="I6" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33307,26 +33269,26 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="12">
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="H7" s="13" t="s">
         <v>84</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>85</v>
       </c>
       <c r="I7" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33339,26 +33301,26 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="12">
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="I8" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33371,26 +33333,26 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="12">
         <v>10</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I9" s="14" t="str">
         <f t="shared" si="0"/>
@@ -33423,26 +33385,26 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="12">
         <v>8</v>
       </c>
       <c r="F10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="H10" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="I10" s="14" t="str">
         <f t="shared" si="0"/>
